--- a/서버정보/20260821_리소스배포_개발.xlsx
+++ b/서버정보/20260821_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3858C8A2-84C6-41FF-9CA3-59E53213B839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51B2C5F-CFC6-4684-8B1F-A897CD6BFE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -2422,10 +2422,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2440,11 +2437,24 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2983,16 +2993,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3007,46 +3007,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF58" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF58" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="B1:AF58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="30">
       <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="25"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="23"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="26"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="24"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="18">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="15"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="14"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="13"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="11">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="14"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="12">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8904,6 +8904,7 @@
       <c r="AF53" s="1"/>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A54" s="43"/>
       <c r="B54" s="1" t="s">
         <v>31</v>
       </c>
@@ -8991,6 +8992,7 @@
       <c r="AF54" s="1"/>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A55" s="43"/>
       <c r="B55" s="1" t="s">
         <v>31</v>
       </c>
@@ -9078,6 +9080,7 @@
       <c r="AF55" s="1"/>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A56" s="43"/>
       <c r="B56" s="1" t="s">
         <v>31</v>
       </c>
@@ -9165,6 +9168,7 @@
       <c r="AF56" s="1"/>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A57" s="43"/>
       <c r="B57" s="1" t="s">
         <v>31</v>
       </c>
@@ -9252,6 +9256,7 @@
       <c r="AF57" s="1"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A58" s="43"/>
       <c r="B58" s="1" t="s">
         <v>405</v>
       </c>
@@ -9259,7 +9264,7 @@
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>IF</v>
       </c>
-      <c r="D58" s="38" t="s">
+      <c r="D58" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -9292,7 +9297,7 @@
       <c r="N58" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="O58" s="38" t="str">
+      <c r="O58" s="1" t="str">
         <f>SUBSTITUTE(F58,"hazr-","")&amp;"-osdisk"</f>
         <v>d-if-edmsstr01-osdisk</v>
       </c>
@@ -9302,10 +9307,10 @@
       <c r="Q58" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="R58" s="38"/>
+      <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-      <c r="T58" s="38"/>
-      <c r="U58" s="38" t="str">
+      <c r="T58" s="1"/>
+      <c r="U58" s="1" t="str">
         <f>SUBSTITUTE(F58,"hazr-","")&amp;"-nic"</f>
         <v>d-if-edmsstr01-nic</v>
       </c>
@@ -12286,6 +12291,7 @@
       <c r="R53" s="17"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" s="43"/>
       <c r="B54" s="16" t="s">
         <v>31</v>
       </c>
@@ -15127,46 +15133,47 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B75" s="43" t="s">
+      <c r="A75" s="37"/>
+      <c r="B75" s="42" t="s">
         <v>405</v>
       </c>
-      <c r="C75" s="43" t="s">
+      <c r="C75" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="D75" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="E75" s="40" t="str">
+      <c r="D75" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E75" s="39" t="str">
         <f t="shared" si="4"/>
         <v>d-if-edmsstr01-nsg</v>
       </c>
-      <c r="F75" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="G75" s="40" t="s">
+      <c r="F75" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="H75" s="40" t="s">
+      <c r="H75" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="I75" s="39" t="s">
+      <c r="I75" s="38" t="s">
         <v>406</v>
       </c>
-      <c r="J75" s="42" t="s">
+      <c r="J75" s="41" t="s">
         <v>414</v>
       </c>
-      <c r="K75" s="40" t="str">
+      <c r="K75" s="39" t="str">
         <f t="shared" si="5"/>
         <v>d-if-edmsstr01-nic</v>
       </c>
-      <c r="L75" s="41" t="s">
+      <c r="L75" s="40" t="s">
         <v>413</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E75">
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15184,12 +15191,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -15333,6 +15334,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -15342,22 +15349,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15373,4 +15364,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>